--- a/MBExcelData/MBData.xlsx
+++ b/MBExcelData/MBData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpattel\eclipse-workspace\Learning\MagicBricks\MBExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D7A1A2-7E5A-444B-A933-C6E8760D2C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE124E8-B83E-4417-A66D-9B8EDD3258C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -350,6 +350,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">

--- a/MBExcelData/MBData.xlsx
+++ b/MBExcelData/MBData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUBINDU\eclipse-workspace\MagicBricks\MBExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7A0B0E-94C5-4069-ACBB-A6384C0FC8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF38C208-C2A3-4CD2-BA73-9156232C6240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>Bangalore</t>
+    <t>Capgemini</t>
   </si>
 </sst>
 </file>

--- a/MBExcelData/MBData.xlsx
+++ b/MBExcelData/MBData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KS89\git\repository2\MagicBricks\MBExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5124D76-2949-432D-A50A-6BBF9F028433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57A4018-65BF-4F2B-A9F0-421A51494A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="1820" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>BASE URL:</t>
   </si>
@@ -35,12 +35,30 @@
   <si>
     <t>https://www.magicbricks.com/home-interior/1bhk-interior-design?inc=topnavigation</t>
   </si>
+  <si>
+    <t>Vicky</t>
+  </si>
+  <si>
+    <r>
+      <t>kp24</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF2A00FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>@gmail.com</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,6 +67,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color rgb="FF2A00FF"/>
       <name val="Consolas"/>
@@ -358,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.26953125" customWidth="1"/>
@@ -379,6 +404,16 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MBExcelData/MBData.xlsx
+++ b/MBExcelData/MBData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpattel\eclipse-workspace\Learning\MagicBricks\MBExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE124E8-B83E-4417-A66D-9B8EDD3258C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED0A41B-0DBC-45AD-A825-D36848AD8C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>BaseURL</t>
+    <t>https://www.magicbricks.com/</t>
   </si>
   <si>
-    <t>https://www.magicbricks.com/</t>
+    <t>Jawahar</t>
+  </si>
+  <si>
+    <t>SBI Home Loan Highlights</t>
   </si>
 </sst>
 </file>
@@ -348,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -356,12 +359,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/MBExcelData/MBData.xlsx
+++ b/MBExcelData/MBData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KS89\git\repository2\MagicBricks\MBExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57A4018-65BF-4F2B-A9F0-421A51494A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABAAF02-F73B-4BCA-AFFE-63E3E991B150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1820" yWindow="1820" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>BASE URL:</t>
   </si>
@@ -36,29 +36,14 @@
     <t>https://www.magicbricks.com/home-interior/1bhk-interior-design?inc=topnavigation</t>
   </si>
   <si>
-    <t>Vicky</t>
-  </si>
-  <si>
-    <r>
-      <t>kp24</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF2A00FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>@gmail.com</t>
-    </r>
+    <t>Krishna</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,13 +52,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF2A00FF"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <u/>
       <sz val="10"/>
       <color rgb="FF2A00FF"/>
       <name val="Consolas"/>
@@ -410,9 +388,7 @@
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
